--- a/samples/outputs/XQ-4165884_parsed.xlsx
+++ b/samples/outputs/XQ-4165884_parsed.xlsx
@@ -115,6 +115,12 @@
   </x:si>
   <x:si>
     <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term-Months</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term in months</x:t>
   </x:si>
   <x:si>
     <x:t>FLEX-CST-CR</x:t>
@@ -540,7 +546,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AA14"/>
+  <x:dimension ref="A1:AA15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:27">
@@ -683,22 +689,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K4" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="T4" s="0">
-        <x:v>85</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="U4" s="0">
-        <x:v>100</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="V4" s="0">
         <x:v>1</x:v>
@@ -712,25 +718,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="F5" s="0">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K5" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="0">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="S5" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="T5" s="0">
-        <x:v>34294.5</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="U5" s="0">
-        <x:v>38105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="V5" s="0">
         <x:v>1</x:v>
@@ -750,7 +759,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K6" s="0">
         <x:v>5</x:v>
@@ -759,10 +768,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T6" s="0">
-        <x:v>3096</x:v>
+        <x:v>34294.5</x:v>
       </x:c>
       <x:c r="U6" s="0">
-        <x:v>3440</x:v>
+        <x:v>38105</x:v>
       </x:c>
       <x:c r="V6" s="0">
         <x:v>1</x:v>
@@ -776,10 +785,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>3</x:v>
@@ -814,7 +823,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K8" s="0">
         <x:v>5</x:v>
@@ -823,10 +832,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T8" s="0">
-        <x:v>8982</x:v>
+        <x:v>3096</x:v>
       </x:c>
       <x:c r="U8" s="0">
-        <x:v>9980</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="V8" s="0">
         <x:v>1</x:v>
@@ -846,7 +855,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K9" s="0">
         <x:v>5</x:v>
@@ -855,10 +864,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T9" s="0">
-        <x:v>3370.5</x:v>
+        <x:v>8982</x:v>
       </x:c>
       <x:c r="U9" s="0">
-        <x:v>3745</x:v>
+        <x:v>9980</x:v>
       </x:c>
       <x:c r="V9" s="0">
         <x:v>1</x:v>
@@ -878,7 +887,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K10" s="0">
         <x:v>5</x:v>
@@ -887,10 +896,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T10" s="0">
-        <x:v>26355</x:v>
+        <x:v>3370.5</x:v>
       </x:c>
       <x:c r="U10" s="0">
-        <x:v>28875</x:v>
+        <x:v>3745</x:v>
       </x:c>
       <x:c r="V10" s="0">
         <x:v>1</x:v>
@@ -919,10 +928,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>26355</x:v>
       </x:c>
       <x:c r="U11" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>28875</x:v>
       </x:c>
       <x:c r="V11" s="0">
         <x:v>1</x:v>
@@ -951,10 +960,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T12" s="0">
-        <x:v>2079</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="U12" s="0">
-        <x:v>2310</x:v>
+        <x:v>1E-06</x:v>
       </x:c>
       <x:c r="V12" s="0">
         <x:v>1</x:v>
@@ -983,21 +992,53 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T13" s="0">
+        <x:v>2079</x:v>
+      </x:c>
+      <x:c r="U13" s="0">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="V13" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:27">
+      <x:c r="A14" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F14" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S14" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T14" s="0">
         <x:v>61236</x:v>
       </x:c>
-      <x:c r="U13" s="0">
+      <x:c r="U14" s="0">
         <x:v>68040</x:v>
       </x:c>
-      <x:c r="V13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:27">
-      <x:c r="B14" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>53</x:v>
+      <x:c r="V14" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:27">
+      <x:c r="B15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/samples/outputs/XQ-4165884_parsed.xlsx
+++ b/samples/outputs/XQ-4165884_parsed.xlsx
@@ -701,10 +701,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V4" s="0">
         <x:v>1</x:v>
@@ -960,10 +960,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T12" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U12" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V12" s="0">
         <x:v>1</x:v>
